--- a/Taxonomy_tables_v3.3.xlsx
+++ b/Taxonomy_tables_v3.3.xlsx
@@ -845,7 +845,7 @@
     <t>LDD</t>
   </si>
   <si>
-    <t xml:space="preserve"> LDD(sys_a;sys_b), different types of LLRS in the two directions
+    <t>LDD(sys_a;sys_b), different types of LLRS in the two directions
 (a= system parallel to the building facade;
  b= system perpendicular to the building facade)</t>
   </si>
